--- a/data/trans_orig/P1411-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2012</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60632</t>
+          <t>59933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89646</t>
+          <t>89315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914011</t>
+          <t>914710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>943621</t>
+          <t>943364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1299098</t>
+          <t>1297947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1319141</t>
+          <t>1318222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2221611</t>
+          <t>2221942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2256866</t>
+          <t>2256961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34886</t>
+          <t>34986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>44423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1929071</t>
+          <t>1928971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1949598</t>
+          <t>1949586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1738267</t>
+          <t>1737086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750496</t>
+          <t>1750351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3674346</t>
+          <t>3674126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3697303</t>
+          <t>3696638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469787</t>
+          <t>468628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479271</t>
+          <t>479294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450643</t>
+          <t>450584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924894</t>
+          <t>923928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936751</t>
+          <t>936761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53907</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>90725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>52861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>89239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132938</t>
+          <t>132177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3329798</t>
+          <t>3329057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3365875</t>
+          <t>3364510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3497340</t>
+          <t>3496976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3522462</t>
+          <t>3522406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6836681</t>
+          <t>6837442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6880178</t>
+          <t>6880380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2016</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21225</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>46076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51148</t>
+          <t>51650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84944</t>
+          <t>85610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706666</t>
+          <t>706805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729418</t>
+          <t>729701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>949733</t>
+          <t>948584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>973435</t>
+          <t>972930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1664063</t>
+          <t>1663397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1697859</t>
+          <t>1697357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43547</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55548</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2032838</t>
+          <t>2031500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054901</t>
+          <t>2054731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1971217</t>
+          <t>1970500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1984369</t>
+          <t>1984085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4009137</t>
+          <t>4009204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4035859</t>
+          <t>4035231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541074</t>
+          <t>539495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539317</t>
+          <t>539153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548135</t>
+          <t>548137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084404</t>
+          <t>1084002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094148</t>
+          <t>1094022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52024</t>
+          <t>52466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84498</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>59873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>92744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135266</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3293120</t>
+          <t>3292189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3325594</t>
+          <t>3325152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3474433</t>
+          <t>3472227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499682</t>
+          <t>3500311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6774452</t>
+          <t>6775103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6818202</t>
+          <t>6816974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1411-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59933</t>
+          <t>59088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>53856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89315</t>
+          <t>89710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914710</t>
+          <t>915555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>943364</t>
+          <t>943995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1297947</t>
+          <t>1297694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1318222</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2221942</t>
+          <t>2221547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2256961</t>
+          <t>2257401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1928971</t>
+          <t>1929072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1949586</t>
+          <t>1949555</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1737086</t>
+          <t>1738813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750351</t>
+          <t>1751282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3674126</t>
+          <t>3674003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3696638</t>
+          <t>3698454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468628</t>
+          <t>469697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479294</t>
+          <t>479207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450584</t>
+          <t>450668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>923928</t>
+          <t>924451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936761</t>
+          <t>936593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55272</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90725</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52861</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89239</t>
+          <t>91366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132177</t>
+          <t>134053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3329057</t>
+          <t>3329073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3364510</t>
+          <t>3364057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3496976</t>
+          <t>3498260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3522406</t>
+          <t>3522982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6837442</t>
+          <t>6835566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6880380</t>
+          <t>6878253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46076</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51650</t>
+          <t>51404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85610</t>
+          <t>83672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706805</t>
+          <t>707985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>729701</t>
+          <t>729349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>948584</t>
+          <t>947978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>972930</t>
+          <t>972199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1663397</t>
+          <t>1665335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1697357</t>
+          <t>1697603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29454</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2031500</t>
+          <t>2033032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054731</t>
+          <t>2055306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1970500</t>
+          <t>1970313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1984085</t>
+          <t>1984314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4009204</t>
+          <t>4008887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4035231</t>
+          <t>4035679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539495</t>
+          <t>540250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539153</t>
+          <t>539051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548137</t>
+          <t>548141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084002</t>
+          <t>1084026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094022</t>
+          <t>1094023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52466</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85429</t>
+          <t>85800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92744</t>
+          <t>92793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134615</t>
+          <t>134715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3292189</t>
+          <t>3291818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3325152</t>
+          <t>3325540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3472227</t>
+          <t>3471627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3500311</t>
+          <t>3500479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6775103</t>
+          <t>6775003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6816974</t>
+          <t>6816925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
